--- a/AAII_Financials/Yearly/ADTN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ADTN_YR_FIN.xlsx
@@ -2273,7 +2273,7 @@
         <v>193300</v>
       </c>
       <c r="F43" s="3">
-        <v>234700</v>
+        <v>223300</v>
       </c>
       <c r="G43" s="3">
         <v>300300</v>
@@ -2324,7 +2324,7 @@
         <v>261600</v>
       </c>
       <c r="F44" s="3">
-        <v>362300</v>
+        <v>360400</v>
       </c>
       <c r="G44" s="3">
         <v>427500</v>
@@ -2426,7 +2426,7 @@
         <v>599100</v>
       </c>
       <c r="F46" s="3">
-        <v>736900</v>
+        <v>719000</v>
       </c>
       <c r="G46" s="3">
         <v>882400</v>
@@ -2528,7 +2528,7 @@
         <v>136800</v>
       </c>
       <c r="F48" s="3">
-        <v>151100</v>
+        <v>155600</v>
       </c>
       <c r="G48" s="3">
         <v>141000</v>
@@ -2579,7 +2579,7 @@
         <v>337800</v>
       </c>
       <c r="F49" s="3">
-        <v>690800</v>
+        <v>695600</v>
       </c>
       <c r="G49" s="3">
         <v>782900</v>
@@ -2732,7 +2732,7 @@
         <v>78800</v>
       </c>
       <c r="F52" s="3">
-        <v>77000</v>
+        <v>76800</v>
       </c>
       <c r="G52" s="3">
         <v>59600</v>
@@ -2834,7 +2834,7 @@
         <v>1171400</v>
       </c>
       <c r="F54" s="3">
-        <v>1682500</v>
+        <v>1677400</v>
       </c>
       <c r="G54" s="3">
         <v>1943500</v>
@@ -3029,7 +3029,7 @@
         <v>54600</v>
       </c>
       <c r="F59" s="3">
-        <v>58400</v>
+        <v>54100</v>
       </c>
       <c r="G59" s="3">
         <v>57400</v>
@@ -3080,7 +3080,7 @@
         <v>293500</v>
       </c>
       <c r="F60" s="3">
-        <v>278100</v>
+        <v>274000</v>
       </c>
       <c r="G60" s="3">
         <v>428600</v>
@@ -3386,7 +3386,7 @@
         <v>621500</v>
       </c>
       <c r="F66" s="3">
-        <v>635500</v>
+        <v>628900</v>
       </c>
       <c r="G66" s="3">
         <v>639900</v>
@@ -3662,7 +3662,7 @@
         <v>-688800</v>
       </c>
       <c r="F72" s="3">
-        <v>-232900</v>
+        <v>-231700</v>
       </c>
       <c r="G72" s="3">
         <v>55300</v>
@@ -3866,7 +3866,7 @@
         <v>127000</v>
       </c>
       <c r="F76" s="3">
-        <v>604800</v>
+        <v>605300</v>
       </c>
       <c r="G76" s="3">
         <v>974000</v>
